--- a/data/daily/2026-10/2026-10-30.xlsx
+++ b/data/daily/2026-10/2026-10-30.xlsx
@@ -2084,21 +2084,21 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16386</v>
+        <v>16388</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>확실한 피로 회복과 활력 — 복용 시 몸이 가벼워지고 피로 회복과 활력 충전에 효과적임</t>
+          <t>고급스러운 선물 패키지 — 기프트박스 포장이 고급스러워 선물용으로 받고 전하기에 제격임</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 기프트박스 포장과 사은품 구성이 고급스러워 선물용으로 적합함</t>
+          <t>피로 회복 및 활력 충전 — 섭취 후 피로가 해소되고 몸이 가벼워지며 활력이 생기는 것을 체감함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>물 없이도 간편한 섭취 — 상단 정제와 고농축 액상 구성으로 물 없이 어디서나 간편하게 섭취 가능함</t>
+          <t>물 없이 먹는 듀얼 포뮬러 — 정제와 고농축 액상으로 이루어져 어디서나 물 없이 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2147,22 +2147,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>알찬 영양 성분 구성 — 멀티비타민과 미네랄을 한 번에 챙길 수 있고 10입 단위 구성이 무난함</t>
+          <t>부담 없는 10입 단위 수량 — 10입 박스 단위 구성으로 대용량보다 고르기 편하고 무난함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 개별 포장과 휴대 — 액상과 정제가 함께 들어간 개별 포장으로 휴대 및 섭취가 간편함</t>
+          <t>액상과 정제 개별 포장 — 액상과 정제가 함께 들어있는 개별 포장이라 휴대와 챙겨 먹기가 편리함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>합리적인 가격과 깔끔함 — 가격대가 적절하며 포장이 깔끔하고 키링 사은품이 포함되어 실용적임</t>
+          <t>합리적인 가격과 증정품 — 가격대가 괜찮고 실용적인 키링 사은품이 동봉되어 만족스러움</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>선물용 쇼핑백 미제공 — 선물용 쇼핑백이 따로 동봉되어 오지 않아 아쉬움</t>
+          <t>선물용 쇼핑백 미동봉 — 제품 단품으로만 배송되고 별도 쇼핑백이 제공되지 않는 점이 아쉬움</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -2206,26 +2206,26 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3431</v>
+        <v>3433</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>하루 한 병의 간편 케어 — 여러 영양제를 따로 챙길 필요 없이 하루 한 병으로 섭취 가능함</t>
+          <t>하루 한 병 간편한 복용 — 하루 한 병으로 영양소를 다 챙길 수 있어 복용 편의성이 뛰어남</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>넉넉한 용량과 진한 액상 — 30+3입의 넉넉한 구성에 액상 농도가 진하여 만족스러움</t>
+          <t>넉넉한 30+3입 구성 — 한 달 넘게 먹을 수 있는 넉넉한 수량으로 온 가족이 나누어 먹기 좋음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 인지도 높은 고품질 비타민으로 패키지가 예뻐 선물 만족도가 높음</t>
+          <t>에너지 충전과 편안한 속 — 복용 후 활력이 생기고 속이 편안해 기운을 얻기에 좋음</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>부담스러운 높은 가격 — 제품 품질에 비해 가격대가 다소 비싸게 형성됨</t>
+          <t>다소 부담스러운 가격대 — 유명하고 고품질인 만큼 가격에 대한 부담이 일부 존재함</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2273,17 +2273,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 구미 제형의 편의 — 지나치게 달지 않은 과일 향 젤리 형태로 물 없이 간식처럼 섭취함</t>
+          <t>맛있는 젤리 형태 제형 — 약 같은 느낌 없이 달콤하고 상큼한 과일 향 젤리처럼 즐길 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>알약 삼킴 부담 완화 — 알약을 물과 함께 삼킬 필요가 없어 영양제 섭취 거부감이 적음</t>
+          <t>물 없이 먹는 섭취 편의성 — 물 없이 간식처럼 하루 알맞게 씹어 먹을 수 있어 꾸준히 챙기기 용이함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>남녀노소 즐기는 넉넉함 — 80구미 용량으로 넉넉하며 누구나 부담 없이 먹을 수 있음</t>
+          <t>부담 없는 선물용 구성 — 남녀노소 누구나 즐길 수 있고 상큼한 포장으로 선물에 적합함</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2332,15 +2332,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>액상과 정제의 이중 구성 — 비타민 알약과 액상이 함께 들어 있어 시너지 효과를 기대하게 함</t>
+          <t>액상 정제 이중 구성 — 알약과 액상을 함께 마시는 구조라 영양 섭취 효과가 높게 느껴짐</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>체력 관리와 피로 회복 — 환절기 건강 관리나 바쁜 일상 속 체력 유지에 큰 도움이 됨</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>환절기 및 피로 관리 — 개강이나 환절기 등 체력 유지가 필요할 때 상쾌하게 컨디션을 케어해 줌</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>만족스러운 포장과 배송 — 필요한 시기에 맞춘 빠른 배송과 알찬 선물 에디션 구성을 갖춤</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2383,19 +2387,23 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>8773</v>
+        <v>8774</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>증정품 포함 알찬 구성 — 7입 구성에 2입이 추가 증정되어 넉넉하게 복용 가능함</t>
+          <t>실속 있는 추가 증정 구성 — 7입 구성에 2입이 추가 증정되어 아홉 개로 유용하게 이용 가능함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>착한 가격과 간편한 섭취 — 착한 가격대에 구매 가능하며 간편하게 하루 활력을 챙김</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>넉넉하고 긴 유통기한 — 유통기한이 길어서 개봉 시점이 늦어져도 안심하고 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>착한 가격과 가성비 — 좋은 비타민 제품을 합리적인 가격에 구매할 수 있어 가성비가 높음</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2438,29 +2446,25 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>개별 포 형태의 편리함 — 컴팩트한 포 형태로 되어 있어 가방에 넣고 다니며 챙겨 먹기 좋음</t>
+          <t>휴대성 높은 멀티팩 포장 — 컴팩트한 포 형태로 되어 있어 가방에 넣거나 여행 시 챙겨 가기 편리함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>깔끔한 포장과 빠른 배송 — 포장이 깔끔하고 배송이 빠르며 선물용으로 적합함</t>
+          <t>간편한 일일 영양 관리 — 한 포씩 꺼내 먹는 간편함으로 활력 증진 및 피로 해소에 도움이 됨</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>배송 과정 중 박스 구김 — 배송 시 제품 외관 박스가 구겨져서 도착함</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>아쉬운 사은품 품질 — 동봉되어 온 사은품의 구성이나 품질이 기대에 미치지 못함</t>
-        </is>
-      </c>
+          <t>배송 시 박스 훼손 발생 — 배송 과정에서 제품 박스가 구겨져서 도착하는 아쉬움이 있음</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
@@ -2501,21 +2505,21 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>목걸림 없는 가루 제형 — 눌러서 분말을 액상에 풀어 마시는 형태로 알약 목걸림 불편이 없음</t>
+          <t>독특한 분말 섞기 섭취법 — 용기를 눌러 분말을 액상에 풀어 마시는 신기하고 간편한 방식임</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>우수한 활력 증진 효과 — 섭취 후 피로가 완화되고 빠른 활력 충전 효과를 체감함</t>
+          <t>알약 걸림 없는 목넘김 — 알약 형태가 아니어서 목에 이물감이나 걸림 없이 편하게 복용함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>신뢰도 높은 고급 포장 — 정관장 브랜드 신뢰도가 높고 고급스러운 포장으로 선물하기 좋음</t>
+          <t>확실한 활력 증진 효과 — 피곤할 때 마시면 활력이 생기고 기운이 나는 효과가 체감됨</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -2564,18 +2568,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>확실한 활력 충전 효과 — 바쁜 일정 전에 복용 시 체력 증진과 활력에 확실한 도움을 줌</t>
+          <t>빠른 체력 및 활력 보충 — 바쁘거나 지칠 때 미리 복용하면 확실하게 활력이 도는 것을 느낌</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>정성스러운 선물용 구성 — 배송 상태가 양호하며 정성스러운 마음을 전하기 좋은 선물임</t>
+          <t>신속한 배송 서비스 — 배송 상태가 양호하며 빠르게 받아볼 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>감기약 맛에 대한 호불호 — 오렌지 맛 감기약 느낌이 나 맛에 대한 호불호가 갈릴 수 있음</t>
+          <t>호불호 있는 약 맛 — 오렌지 향 감기약 느낌의 강한 맛이 남아 호불호가 나뉠 수 있음</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -2619,26 +2623,26 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>오쏘몰 대비 높은 가성비 — 타사 유명 제품 대비 가격이 실속 있고 효과가 뛰어남</t>
+          <t>높은 가성비와 실속 성분 — 유명 비타민 브랜드 대비 가격이 착하고 성분 구성이 실속 있음</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>빠른 피로 회복과 컨디션 — 아침이나 피곤할 때 섭취 시 커피 없이도 상쾌함과 체력 회복을 도움</t>
+          <t>우수한 피로 회복 체감 — 아침 피로 해소나 컨디션 난조 시 상쾌하게 회복되는 효과를 느낌</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 편리함 — 맛이 괜찮아 수험생 등 남녀노소 한 병씩 간편하게 먹기 좋음</t>
+          <t>휴대하기 편한 병 형태 — 하루 한 병씩 챙겨 다니며 외출 시에도 간편하게 복용 가능함</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>선물용 쇼핑백 누락 — 상품 수령 시 쇼핑백이 동봉되지 않고 누락됨</t>
+          <t>선물용 쇼핑백 누락 — 배송 시 선물에 필요한 쇼핑백이 동봉되지 않아 아쉬움</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -2686,17 +2690,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 상관없이 먹기 좋으며 다음 날 확실하게 숙취를 줄여줌</t>
+          <t>확실한 빠른 숙취 해소 — 음주 전후 섭취 시 다음 날 속이 편안하고 숙취 회복이 빠름</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>15포의 넉넉한 구성 — 5포씩 3박스로 나뉘어 보관이 용이하고 연말 모임에 넉넉하게 사용함</t>
+          <t>위생적인 개별 스틱 포장 — 한 포씩 개별 포장되어 가방에 넣고 다니며 챙겨 먹기 용이함</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>휴대하기 편한 개별 포장 — 깔끔하게 개별 포장되어 가방에 넣고 다니며 챙기기 용이함</t>
+          <t>넉넉한 3박스 세트 구성 — 총 15포의 넉넉한 양과 깔끔한 패키지로 선물하기에도 적합함</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2745,20 +2749,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>우수한 소화 개선 효과 — 식사 후 복용 시 속이 편안해지고 소화가 잘 됨</t>
+          <t>더부룩함 감소 및 소화 지원 — 식사 후 복용 시 속 더부룩함이 사라지고 소화가 잘되도록 도와줌</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>물 없이 먹는 고소한 맛 — 옥수수 맛이라 거부감이 없고 물 없이도 간편하게 섭취 가능함</t>
+          <t>고소한 옥수수 맛 제형 — 옥수수 맛이라 거부감이 없고 물 없이 가루째 섭취하기 편리함</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>만족스러운 사은품 증정 — 추가 포장과 저당 견과류바 등 사은품 혜택이 훌륭함</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>맛있는 견과류바 증정 — 사은품으로 증정되는 저당 견과류바가 고소하고 맛있어 만족함</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>체감 효과의 차이 — 유산균 대용으로 구매 시 즉각적인 효과 체감이 둔할 수 있음</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -2804,22 +2812,18 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>다양하고 맛있는 구성 — 카카오, 크림소다 등 다양한 맛으로 구성되어 맛있게 먹기 좋음</t>
+          <t>풍성한 콜라보 에디션 구성 — 효소 외에 단백질바와 포토카드까지 세트로 들어있어 만족도가 큼</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>단백질바와 포토카드 구성 — 효소와 함께 큼직한 단백질바 및 아이돌 포토카드가 제공됨</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>속을 편안하게 돕는 효소 — 소화나 위 건강 관리에 도움을 주며 영양을 챙길 수 있음</t>
-        </is>
-      </c>
+          <t>다양하고 맛있는 효소 맛 — 베리말차, 크림소다 등 거부감 없는 맛있는 맛이라 지속 복용 가능함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>포토카드 포장 미흡 — 배송 시 포장이 미흡하여 제공된 포토카드가 구겨져서 옴</t>
+          <t>포토카드 구겨짐 발생 — 배송 과정에서 구성품인 포토카드가 다소 구겨져 포장에 주의가 필요함</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -2867,22 +2871,18 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 패키지와 선물 포장이 매우 고급스러워 개봉 시 감동을 줌</t>
+          <t>고급스러운 오간자 패키지 — 오간자 포장 및 플리츠백 구성으로 열어볼 때 감동을 주는 패키지임</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>피부 개선 및 뛰어난 맛 — 맛이 좋으며 꾸준히 복용 시 피부 탄력과 촉촉함 유지에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>앰플 추가 증정 혜택 — 플리츠백과 추가 앰플 구성으로 알차고 유용함</t>
-        </is>
-      </c>
+          <t>맛있는 액상 앰플 형태 — 거부감 없는 상큼한 맛으로 하루 한 병씩 챙겨 마시기 편함</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>오간자 포장 옵션 누락 — 안내된 오간자 포장이 적용되지 않은 채로 배송됨</t>
+          <t>오간자 포장 누락 배송 — 일부 제품 배송 시 안내된 오간자 포장이 누락되어 배송되는 경우가 있음</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -2930,17 +2930,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 더부룩한 속을 줄여주고 식후 소화를 원활하게 도와줌</t>
+          <t>식후 속 더부룩함 개선 — 밀가루나 과식 후 복용 시 속이 편안해지고 소화가 잘됨</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>미숫가루 같은 고소한 맛 — 텁텁하지 않고 고소한 맛으로 거부감 없이 섭취 가능함</t>
+          <t>고소한 미숫가루 풍미 — 텁텁함 없이 고구마나 미숫가루 같은 고소한 맛이라 거부감이 없음</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>넉넉한 용량과 사은품 — 몇 달간 섭취할 수 있는 양에 견과류 사은품까지 함께 제공됨</t>
+          <t>원활한 배변 활동 도움 — 꾸준히 복용하면 아침 화장실 이용이 편안해져 장 관리에 유용함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2989,17 +2989,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>질리지 않는 20종 구성 — 다양한 맛과 종류로 구성되어 매일 질리지 않고 섭취 가능함</t>
+          <t>질리지 않는 20종 구성 — 다양한 종류로 구성되어 식단 관리 시 물리지 않고 맛있게 먹음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>전자레인지 용기 제공 — 전용 용기를 사은품으로 주어 간편하게 데워 먹기 좋음</t>
+          <t>전자레인지 용기 사은품 — 전용 용기가 증정되어 간단하게 데워 먹기 편리함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>신선한 배송과 가성비 — 아이스팩으로 신선하게 배송되며 가격대가 저렴함</t>
+          <t>촉촉하고 부드러운 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하여 부담 없이 즐기기 좋음</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -3048,17 +3048,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>비린 맛 없는 맛있는 맛 — 비린 맛이나 느끼함 없이 음료처럼 달콤하고 맛있음</t>
+          <t>비린 맛없는 달콤한 맛 — 단백질 특유의 비린 맛 없이 초코딸기 등 맛있는 음료처럼 마심</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>간식 대용의 높은 포만감 — 마셨을 때 은근히 배가 차서 출출할 때 간식용으로 좋음</t>
+          <t>든든한 포만감 유지 — 마신 후 배고픔이 줄어들어 간식이 당길 때 대용으로 좋음</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>운동 후 간편한 단백질 — 운동 후 한 팩씩 마시며 손쉽게 단백질을 보충함</t>
+          <t>운동 후 간편한 단백질 보충 — 운동 직후 한 팩씩 간편하게 마시며 단백질을 보충하기 적합함</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3107,20 +3107,20 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하여 맛있음</t>
+          <t>다양한 맛의 식단 관리 — 여러 맛이 골고루 포함되어 식단 관리 중에도 질리지 않음</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>전자레인지 간편 조리 — 전자레인지에 데우기만 하면 되는 간단한 조리법임</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>질리지 않는 다양한 구성 — 식단 관리에 용이하도록 다양하고 알찬 구성으로 제공됨</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>촉촉한 식감과 조리 편의 — 전자레인지로 쉽게 데워 먹을 수 있으며 고기가 촉촉함</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>동일 브랜드 타 부위 느꺼움 — 같은 브랜드의 닭다리살 제품은 다소 느끼하다는 의견이 존재함</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
@@ -3135,51 +3135,51 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 (아르기닌+글리펌프 1포증정)</t>
+          <t>"닭가슴살 완벽세트" 보냉백+한끼통살 닭가슴살 15팩세트</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/6352718</t>
+          <t>https://gift.kakao.com/product/10892246</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261020094546_5a86ba631cde44229cc1ed845bd1af8f.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260518144708_605bd6c19e8d44cf8257b6dd6cb12c59.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1956</v>
+        <v>20</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>물에 잘 녹는 고운 입자 — 입자가 매우 고와 물에 잘 녹으며 100서빙의 가성비를 자랑함</t>
+          <t>실용적인 넉넉한 보냉백 — 크기가 넉넉한 보냉가방이 동봉되어 도시락으로 들고 다니기 좋음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>운동 수행 능력 향상 — 복용 시 피로가 줄어들고 운동 수행 능력 향상에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>운동인 맞춤 선물 아이템 — 웨이트 트레이닝 등 운동을 즐기는 사람에게 활용도 높음</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>물리지 않는 알찬 입문 구성 — 소세지 포함 다양한 맛이 섞여 있어 질리지 않고 입문용으로 알맞음</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>아토피 등 성분 확인 필요 — 피부 민감 반응이나 아토피가 있는 경우 사전 성분표 확인이 요구됨</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3194,48 +3194,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"35개입" 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 (아르기닌+글리펌프 1포증정)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>45,000원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261020094546_5a86ba631cde44229cc1ed845bd1af8f.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>250</v>
+        <v>1956</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>초고함량 아르기닌 성분 — 1포당 6,200mg의 고함량 아르기닌이 들어 있어 효과적임</t>
+          <t>운동 수행 능력 향상 체감 — 복용 시 운동할 때 덜 피로하고 수행 능력이 향상됨을 느낌</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>체력 증진 및 피로 회복 — 운동 시 지구력과 컨디션을 높여주고 일상 피로를 개선함</t>
+          <t>고운 입자와 뛰어난 용해도 — 입자가 매우 고와 물에 잘 녹으며 100서빙 용량 대비 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>휴대가 간편한 스틱 포장 — 개별 스틱 포장으로 되어 있어 휴대 및 복용이 용이함</t>
+          <t>운동 지인 선물 추천 — 운동을 막 시작하거나 웨이트를 즐기는 지인에게 주기 좋은 선물임</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3560,13 +3560,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16386</v>
+        <v>16388</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>15719</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3431</v>
+        <v>3433</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>6549</v>
@@ -3575,19 +3575,19 @@
         <v>836</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>8773</v>
+        <v>8774</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>792</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -3598,72 +3598,74 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복과 활력 — 복용 시 몸이 가벼워지고 피로 회복과 활력 충전에 효과적임
-고급스러운 선물용 포장 — 기프트박스 포장과 사은품 구성이 고급스러워 선물용으로 적합함
-물 없이도 간편한 섭취 — 상단 정제와 고농축 액상 구성으로 물 없이 어디서나 간편하게 섭취 가능함</t>
+          <t>고급스러운 선물 패키지 — 기프트박스 포장이 고급스러워 선물용으로 받고 전하기에 제격임
+피로 회복 및 활력 충전 — 섭취 후 피로가 해소되고 몸이 가벼워지며 활력이 생기는 것을 체감함
+물 없이 먹는 듀얼 포뮬러 — 정제와 고농축 액상으로 이루어져 어디서나 물 없이 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>알찬 영양 성분 구성 — 멀티비타민과 미네랄을 한 번에 챙길 수 있고 10입 단위 구성이 무난함
-간편한 개별 포장과 휴대 — 액상과 정제가 함께 들어간 개별 포장으로 휴대 및 섭취가 간편함
-합리적인 가격과 깔끔함 — 가격대가 적절하며 포장이 깔끔하고 키링 사은품이 포함되어 실용적임</t>
+          <t>부담 없는 10입 단위 수량 — 10입 박스 단위 구성으로 대용량보다 고르기 편하고 무난함
+액상과 정제 개별 포장 — 액상과 정제가 함께 들어있는 개별 포장이라 휴대와 챙겨 먹기가 편리함
+합리적인 가격과 증정품 — 가격대가 괜찮고 실용적인 키링 사은품이 동봉되어 만족스러움</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>하루 한 병의 간편 케어 — 여러 영양제를 따로 챙길 필요 없이 하루 한 병으로 섭취 가능함
-넉넉한 용량과 진한 액상 — 30+3입의 넉넉한 구성에 액상 농도가 진하여 만족스러움
-선물용으로 높은 만족도 — 인지도 높은 고품질 비타민으로 패키지가 예뻐 선물 만족도가 높음</t>
+          <t>하루 한 병 간편한 복용 — 하루 한 병으로 영양소를 다 챙길 수 있어 복용 편의성이 뛰어남
+넉넉한 30+3입 구성 — 한 달 넘게 먹을 수 있는 넉넉한 수량으로 온 가족이 나누어 먹기 좋음
+에너지 충전과 편안한 속 — 복용 후 활력이 생기고 속이 편안해 기운을 얻기에 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 구미 제형의 편의 — 지나치게 달지 않은 과일 향 젤리 형태로 물 없이 간식처럼 섭취함
-알약 삼킴 부담 완화 — 알약을 물과 함께 삼킬 필요가 없어 영양제 섭취 거부감이 적음
-남녀노소 즐기는 넉넉함 — 80구미 용량으로 넉넉하며 누구나 부담 없이 먹을 수 있음</t>
+          <t>맛있는 젤리 형태 제형 — 약 같은 느낌 없이 달콤하고 상큼한 과일 향 젤리처럼 즐길 수 있음
+물 없이 먹는 섭취 편의성 — 물 없이 간식처럼 하루 알맞게 씹어 먹을 수 있어 꾸준히 챙기기 용이함
+부담 없는 선물용 구성 — 남녀노소 누구나 즐길 수 있고 상큼한 포장으로 선물에 적합함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>액상과 정제의 이중 구성 — 비타민 알약과 액상이 함께 들어 있어 시너지 효과를 기대하게 함
-체력 관리와 피로 회복 — 환절기 건강 관리나 바쁜 일상 속 체력 유지에 큰 도움이 됨</t>
+          <t>액상 정제 이중 구성 — 알약과 액상을 함께 마시는 구조라 영양 섭취 효과가 높게 느껴짐
+환절기 및 피로 관리 — 개강이나 환절기 등 체력 유지가 필요할 때 상쾌하게 컨디션을 케어해 줌
+만족스러운 포장과 배송 — 필요한 시기에 맞춘 빠른 배송과 알찬 선물 에디션 구성을 갖춤</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>증정품 포함 알찬 구성 — 7입 구성에 2입이 추가 증정되어 넉넉하게 복용 가능함
-착한 가격과 간편한 섭취 — 착한 가격대에 구매 가능하며 간편하게 하루 활력을 챙김</t>
+          <t>실속 있는 추가 증정 구성 — 7입 구성에 2입이 추가 증정되어 아홉 개로 유용하게 이용 가능함
+넉넉하고 긴 유통기한 — 유통기한이 길어서 개봉 시점이 늦어져도 안심하고 먹을 수 있음
+착한 가격과 가성비 — 좋은 비타민 제품을 합리적인 가격에 구매할 수 있어 가성비가 높음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>개별 포 형태의 편리함 — 컴팩트한 포 형태로 되어 있어 가방에 넣고 다니며 챙겨 먹기 좋음
-깔끔한 포장과 빠른 배송 — 포장이 깔끔하고 배송이 빠르며 선물용으로 적합함</t>
+          <t>휴대성 높은 멀티팩 포장 — 컴팩트한 포 형태로 되어 있어 가방에 넣거나 여행 시 챙겨 가기 편리함
+간편한 일일 영양 관리 — 한 포씩 꺼내 먹는 간편함으로 활력 증진 및 피로 해소에 도움이 됨</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>목걸림 없는 가루 제형 — 눌러서 분말을 액상에 풀어 마시는 형태로 알약 목걸림 불편이 없음
-우수한 활력 증진 효과 — 섭취 후 피로가 완화되고 빠른 활력 충전 효과를 체감함
-신뢰도 높은 고급 포장 — 정관장 브랜드 신뢰도가 높고 고급스러운 포장으로 선물하기 좋음</t>
+          <t>독특한 분말 섞기 섭취법 — 용기를 눌러 분말을 액상에 풀어 마시는 신기하고 간편한 방식임
+알약 걸림 없는 목넘김 — 알약 형태가 아니어서 목에 이물감이나 걸림 없이 편하게 복용함
+확실한 활력 증진 효과 — 피곤할 때 마시면 활력이 생기고 기운이 나는 효과가 체감됨</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>확실한 활력 충전 효과 — 바쁜 일정 전에 복용 시 체력 증진과 활력에 확실한 도움을 줌
-정성스러운 선물용 구성 — 배송 상태가 양호하며 정성스러운 마음을 전하기 좋은 선물임</t>
+          <t>빠른 체력 및 활력 보충 — 바쁘거나 지칠 때 미리 복용하면 확실하게 활력이 도는 것을 느낌
+신속한 배송 서비스 — 배송 상태가 양호하며 빠르게 받아볼 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰 대비 높은 가성비 — 타사 유명 제품 대비 가격이 실속 있고 효과가 뛰어남
-빠른 피로 회복과 컨디션 — 아침이나 피곤할 때 섭취 시 커피 없이도 상쾌함과 체력 회복을 도움
-부담 없는 맛과 편리함 — 맛이 괜찮아 수험생 등 남녀노소 한 병씩 간편하게 먹기 좋음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>높은 가성비와 실속 성분 — 유명 비타민 브랜드 대비 가격이 착하고 성분 구성이 실속 있음
+우수한 피로 회복 체감 — 아침 피로 해소나 컨디션 난조 시 상쾌하게 회복되는 효과를 느낌
+휴대하기 편한 병 형태 — 하루 한 병씩 챙겨 다니며 외출 시에도 간편하게 복용 가능함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -3672,12 +3674,12 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>선물용 쇼핑백 미제공 — 선물용 쇼핑백이 따로 동봉되어 오지 않아 아쉬움</t>
+          <t>선물용 쇼핑백 미동봉 — 제품 단품으로만 배송되고 별도 쇼핑백이 제공되지 않는 점이 아쉬움</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>부담스러운 높은 가격 — 제품 품질에 비해 가격대가 다소 비싸게 형성됨</t>
+          <t>다소 부담스러운 가격대 — 유명하고 고품질인 만큼 가격에 대한 부담이 일부 존재함</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
@@ -3685,19 +3687,18 @@
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>배송 과정 중 박스 구김 — 배송 시 제품 외관 박스가 구겨져서 도착함
-아쉬운 사은품 품질 — 동봉되어 온 사은품의 구성이나 품질이 기대에 미치지 못함</t>
+          <t>배송 시 박스 훼손 발생 — 배송 과정에서 제품 박스가 구겨져서 도착하는 아쉬움이 있음</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>감기약 맛에 대한 호불호 — 오렌지 맛 감기약 느낌이 나 맛에 대한 호불호가 갈릴 수 있음</t>
+          <t>호불호 있는 약 맛 — 오렌지 향 감기약 느낌의 강한 맛이 남아 호불호가 나뉠 수 있음</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>선물용 쇼핑백 누락 — 상품 수령 시 쇼핑백이 동봉되지 않고 누락됨</t>
+          <t>선물용 쇼핑백 누락 — 배송 시 선물에 필요한 쇼핑백이 동봉되지 않아 아쉬움</t>
         </is>
       </c>
     </row>
@@ -3994,12 +3995,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
           <t>삼대오백</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4052,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t>"닭가슴살 완벽세트" 보냉백+한끼통살 닭가슴살 15팩세트</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 (아르기닌+글리펌프 1포증정)</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>"35개입" 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
     </row>
@@ -4128,10 +4129,10 @@
         <v>75</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>1956</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>250</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4142,72 +4143,68 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 효과 — 음주 전후 상관없이 먹기 좋으며 다음 날 확실하게 숙취를 줄여줌
-15포의 넉넉한 구성 — 5포씩 3박스로 나뉘어 보관이 용이하고 연말 모임에 넉넉하게 사용함
-휴대하기 편한 개별 포장 — 깔끔하게 개별 포장되어 가방에 넣고 다니며 챙기기 용이함</t>
+          <t>확실한 빠른 숙취 해소 — 음주 전후 섭취 시 다음 날 속이 편안하고 숙취 회복이 빠름
+위생적인 개별 스틱 포장 — 한 포씩 개별 포장되어 가방에 넣고 다니며 챙겨 먹기 용이함
+넉넉한 3박스 세트 구성 — 총 15포의 넉넉한 양과 깔끔한 패키지로 선물하기에도 적합함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>우수한 소화 개선 효과 — 식사 후 복용 시 속이 편안해지고 소화가 잘 됨
-물 없이 먹는 고소한 맛 — 옥수수 맛이라 거부감이 없고 물 없이도 간편하게 섭취 가능함
-만족스러운 사은품 증정 — 추가 포장과 저당 견과류바 등 사은품 혜택이 훌륭함</t>
+          <t>더부룩함 감소 및 소화 지원 — 식사 후 복용 시 속 더부룩함이 사라지고 소화가 잘되도록 도와줌
+고소한 옥수수 맛 제형 — 옥수수 맛이라 거부감이 없고 물 없이 가루째 섭취하기 편리함
+맛있는 견과류바 증정 — 사은품으로 증정되는 저당 견과류바가 고소하고 맛있어 만족함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>다양하고 맛있는 구성 — 카카오, 크림소다 등 다양한 맛으로 구성되어 맛있게 먹기 좋음
-단백질바와 포토카드 구성 — 효소와 함께 큼직한 단백질바 및 아이돌 포토카드가 제공됨
-속을 편안하게 돕는 효소 — 소화나 위 건강 관리에 도움을 주며 영양을 챙길 수 있음</t>
+          <t>풍성한 콜라보 에디션 구성 — 효소 외에 단백질바와 포토카드까지 세트로 들어있어 만족도가 큼
+다양하고 맛있는 효소 맛 — 베리말차, 크림소다 등 거부감 없는 맛있는 맛이라 지속 복용 가능함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 패키지와 선물 포장이 매우 고급스러워 개봉 시 감동을 줌
-피부 개선 및 뛰어난 맛 — 맛이 좋으며 꾸준히 복용 시 피부 탄력과 촉촉함 유지에 도움을 줌
-앰플 추가 증정 혜택 — 플리츠백과 추가 앰플 구성으로 알차고 유용함</t>
+          <t>고급스러운 오간자 패키지 — 오간자 포장 및 플리츠백 구성으로 열어볼 때 감동을 주는 패키지임
+맛있는 액상 앰플 형태 — 거부감 없는 상큼한 맛으로 하루 한 병씩 챙겨 마시기 편함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 효과 — 더부룩한 속을 줄여주고 식후 소화를 원활하게 도와줌
-미숫가루 같은 고소한 맛 — 텁텁하지 않고 고소한 맛으로 거부감 없이 섭취 가능함
-넉넉한 용량과 사은품 — 몇 달간 섭취할 수 있는 양에 견과류 사은품까지 함께 제공됨</t>
+          <t>식후 속 더부룩함 개선 — 밀가루나 과식 후 복용 시 속이 편안해지고 소화가 잘됨
+고소한 미숫가루 풍미 — 텁텁함 없이 고구마나 미숫가루 같은 고소한 맛이라 거부감이 없음
+원활한 배변 활동 도움 — 꾸준히 복용하면 아침 화장실 이용이 편안해져 장 관리에 유용함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>질리지 않는 20종 구성 — 다양한 맛과 종류로 구성되어 매일 질리지 않고 섭취 가능함
-전자레인지 용기 제공 — 전용 용기를 사은품으로 주어 간편하게 데워 먹기 좋음
-신선한 배송과 가성비 — 아이스팩으로 신선하게 배송되며 가격대가 저렴함</t>
+          <t>질리지 않는 20종 구성 — 다양한 종류로 구성되어 식단 관리 시 물리지 않고 맛있게 먹음
+전자레인지 용기 사은품 — 전용 용기가 증정되어 간단하게 데워 먹기 편리함
+촉촉하고 부드러운 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하여 부담 없이 즐기기 좋음</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 맛있는 맛 — 비린 맛이나 느끼함 없이 음료처럼 달콤하고 맛있음
-간식 대용의 높은 포만감 — 마셨을 때 은근히 배가 차서 출출할 때 간식용으로 좋음
-운동 후 간편한 단백질 — 운동 후 한 팩씩 마시며 손쉽게 단백질을 보충함</t>
+          <t>비린 맛없는 달콤한 맛 — 단백질 특유의 비린 맛 없이 초코딸기 등 맛있는 음료처럼 마심
+든든한 포만감 유지 — 마신 후 배고픔이 줄어들어 간식이 당길 때 대용으로 좋음
+운동 후 간편한 단백질 보충 — 운동 직후 한 팩씩 간편하게 마시며 단백질을 보충하기 적합함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 식감 — 닭가슴살이 퍽퍽하지 않고 촉촉하여 맛있음
-전자레인지 간편 조리 — 전자레인지에 데우기만 하면 되는 간단한 조리법임
-질리지 않는 다양한 구성 — 식단 관리에 용이하도록 다양하고 알찬 구성으로 제공됨</t>
+          <t>다양한 맛의 식단 관리 — 여러 맛이 골고루 포함되어 식단 관리 중에도 질리지 않음
+촉촉한 식감과 조리 편의 — 전자레인지로 쉽게 데워 먹을 수 있으며 고기가 촉촉함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>물에 잘 녹는 고운 입자 — 입자가 매우 고와 물에 잘 녹으며 100서빙의 가성비를 자랑함
-운동 수행 능력 향상 — 복용 시 피로가 줄어들고 운동 수행 능력 향상에 도움을 줌
-운동인 맞춤 선물 아이템 — 웨이트 트레이닝 등 운동을 즐기는 사람에게 활용도 높음</t>
+          <t>실용적인 넉넉한 보냉백 — 크기가 넉넉한 보냉가방이 동봉되어 도시락으로 들고 다니기 좋음
+물리지 않는 알찬 입문 구성 — 소세지 포함 다양한 맛이 섞여 있어 질리지 않고 입문용으로 알맞음</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>초고함량 아르기닌 성분 — 1포당 6,200mg의 고함량 아르기닌이 들어 있어 효과적임
-체력 증진 및 피로 회복 — 운동 시 지구력과 컨디션을 높여주고 일상 피로를 개선함
-휴대가 간편한 스틱 포장 — 개별 스틱 포장으로 되어 있어 휴대 및 복용이 용이함</t>
+          <t>운동 수행 능력 향상 체감 — 복용 시 운동할 때 덜 피로하고 수행 능력이 향상됨을 느낌
+고운 입자와 뛰어난 용해도 — 입자가 매우 고와 물에 잘 녹으며 100서빙 용량 대비 가성비가 훌륭함
+운동 지인 선물 추천 — 운동을 막 시작하거나 웨이트를 즐기는 지인에게 주기 좋은 선물임</t>
         </is>
       </c>
     </row>
@@ -4218,22 +4215,34 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>체감 효과의 차이 — 유산균 대용으로 구매 시 즉각적인 효과 체감이 둔할 수 있음</t>
+        </is>
+      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>포토카드 포장 미흡 — 배송 시 포장이 미흡하여 제공된 포토카드가 구겨져서 옴</t>
+          <t>포토카드 구겨짐 발생 — 배송 과정에서 구성품인 포토카드가 다소 구겨져 포장에 주의가 필요함</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>오간자 포장 옵션 누락 — 안내된 오간자 포장이 적용되지 않은 채로 배송됨</t>
+          <t>오간자 포장 누락 배송 — 일부 제품 배송 시 안내된 오간자 포장이 누락되어 배송되는 경우가 있음</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>동일 브랜드 타 부위 느꺼움 — 같은 브랜드의 닭다리살 제품은 다소 느끼하다는 의견이 존재함</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>아토피 등 성분 확인 필요 — 피부 민감 반응이나 아토피가 있는 경우 사전 성분표 확인이 요구됨</t>
+        </is>
+      </c>
       <c r="L21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
@@ -4284,12 +4293,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t>29,900원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>17,900원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>45,000원</t>
         </is>
       </c>
     </row>
@@ -4487,27 +4496,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>판도라 브이펌킨티 14개입 (2주분)</t>
+          <t>CJ 한뿌리 흑삼지천보 진녹 30포 (1개월분) (온)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>한뿌리</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22,700원</t>
+          <t>125,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000001001703&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247763&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0100/A00000100170304ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024776301ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -4530,27 +4539,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261662&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026166204ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -4565,7 +4574,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4573,27 +4582,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225906&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022590605ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -4659,27 +4668,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492948ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -4745,31 +4754,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[1+1]알디콤 Plus 숙취해소제 21ml 4포입</t>
+          <t>그래니 살라 VPL정 60정(1개월분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>그래니샐러드</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17,300원</t>
+          <t>22,790원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227457&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000253967&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022745735ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025396704ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>76</v>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -4788,46 +4801,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492948ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>목넘김 편한 초소형 캡슐 — 170mg의 매우 작은 캡슐 크기로 가볍게 삼키기 편함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>질과 장 동시 케어 효과 — 식약처 인정 원료로 질과 장 건강을 한 번에 관리 가능함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>귀여운 포켓몬 콜라보 — 랜덤 카드케이스 등 실용적인 굿즈가 동봉되어 만족스러움</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -4843,46 +4844,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+          <t>[1+1]알디콤 Plus 숙취해소제 21ml 4포입</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>17,300원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227457&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022745735ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>부담 없는 최강 가성비 — 타 제품 대비 매우 저렴한 가격으로 장기 복용에 부담이 없음</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>귀여운 캐릭터 콜라보 — 산리오 한교동 카드홀더 등 매력적인 굿즈가 함께 제공됨</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>간편한 개별 포장 섭취 — 개별 포장으로 위생적이며 하루 한 알로 영양 관리가 가능함</t>
-        </is>
-      </c>
+          <t>주량 약한 사람에게 효과적 — 알코올 흡수가 부담스러운 사람도 숙취 걱정 없이 챙겨 먹기 제격임</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -4890,7 +4883,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4898,12 +4891,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비비랩 글루타치온 콜라겐 W 30포 (30일분)</t>
+          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>비비랩</t>
+          <t>헬스헬퍼</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4913,20 +4906,16 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000190808&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237482&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019080819ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>320</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023748215ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -5055,42 +5044,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
     </row>
@@ -5102,52 +5091,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>한뿌리</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>그래니샐러드</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>생활약속</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>알디콤</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>씨제이웰케어</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>비비랩</t>
+          <t>헬스헬퍼</t>
         </is>
       </c>
     </row>
@@ -5159,17 +5148,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>판도라 브이펌킨티 14개입 (2주분)</t>
+          <t>CJ 한뿌리 흑삼지천보 진녹 30포 (1개월분) (온)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>고려은단 메가도스C 비타민C 3000mg 100포 (100일분)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -5179,32 +5168,32 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>그래니 살라 VPL정 60정(1개월분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>[1+1]알디콤 Plus 숙취해소제 21ml 4포입</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>비비랩 글루타치온 콜라겐 W 30포 (30일분)</t>
+          <t>[추성훈 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
         </is>
       </c>
     </row>
@@ -5220,12 +5209,12 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="n">
+        <v>4.4</v>
+      </c>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -5239,14 +5228,14 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="n">
+        <v>76</v>
+      </c>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+      <c r="L7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5259,18 +5248,10 @@
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>목넘김 편한 초소형 캡슐 — 170mg의 매우 작은 캡슐 크기로 가볍게 삼키기 편함
-질과 장 동시 케어 효과 — 식약처 인정 원료로 질과 장 건강을 한 번에 관리 가능함
-귀여운 포켓몬 콜라보 — 랜덤 카드케이스 등 실용적인 굿즈가 동봉되어 만족스러움</t>
-        </is>
-      </c>
+      <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 최강 가성비 — 타 제품 대비 매우 저렴한 가격으로 장기 복용에 부담이 없음
-귀여운 캐릭터 콜라보 — 산리오 한교동 카드홀더 등 매력적인 굿즈가 함께 제공됨
-간편한 개별 포장 섭취 — 개별 포장으로 위생적이며 하루 한 알로 영양 관리가 가능함</t>
+          <t>주량 약한 사람에게 효과적 — 알코올 흡수가 부담스러운 사람도 숙취 걱정 없이 챙겨 먹기 제격임</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
@@ -5300,17 +5281,17 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>22,700원</t>
+          <t>125,000원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -5320,27 +5301,27 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>22,790원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>31,400원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>16,200원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>17,300원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -5433,7 +5414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5470,16 +5451,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -5527,32 +5508,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -5574,6 +5555,25 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
       </c>
     </row>
